--- a/resultsHPC/Quake_10x_Bladder.xlsx
+++ b/resultsHPC/Quake_10x_Bladder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,10 +482,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="B2" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E2" t="n">
         <v>500</v>
@@ -507,21 +507,21 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9959051318939656</v>
+        <v>0.9967112282271737</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9875623760658064</v>
+        <v>0.9905365210203219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>512</v>
+        <v>64</v>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E3" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F3" t="n">
         <v>0.005</v>
@@ -543,13 +543,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9951773856209982</v>
+        <v>0.9959979928628057</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9869246294373669</v>
+        <v>0.9889074804000568</v>
       </c>
     </row>
     <row r="4">
@@ -557,21 +557,21 @@
         <v>128</v>
       </c>
       <c r="B4" t="n">
-        <v>512</v>
+        <v>32</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>&lt;class 'torch_geometric.nn.conv.sage_conv.SAGEConv'&gt;</t>
+          <t>&lt;class 'torch_geometric.nn.conv.gcn_conv.GCNConv'&gt;</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001</v>
+        <v>0.005</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9965232873728967</v>
+        <v>0.9958925658942768</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9768033689383571</v>
+        <v>0.9886696951958643</v>
       </c>
     </row>
   </sheetData>
